--- a/data/trans_bre/P7_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P7_R-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,57; 17,3</t>
+          <t>8,41; 16,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,15; 14,42</t>
+          <t>5,32; 13,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,94; 15,07</t>
+          <t>5,94; 14,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 7,6</t>
+          <t>-4,09; 7,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>42,92; 111,94</t>
+          <t>42,67; 110,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,4; 89,93</t>
+          <t>26,06; 85,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,85; 101,54</t>
+          <t>30,1; 100,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-12,63; 38,16</t>
+          <t>-14,81; 34,79</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,43; 20,23</t>
+          <t>12,28; 20,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,99; 13,32</t>
+          <t>6,07; 13,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,19; 12,5</t>
+          <t>4,78; 11,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,66; 19,49</t>
+          <t>8,48; 19,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>72,35; 147,78</t>
+          <t>69,99; 145,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,22; 83,79</t>
+          <t>30,25; 84,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,95; 89,25</t>
+          <t>26,5; 84,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>57,11; 325,63</t>
+          <t>56,54; 283,04</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,14; 14,73</t>
+          <t>6,13; 14,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,76; 15,8</t>
+          <t>6,74; 15,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,1; 10,01</t>
+          <t>2,18; 10,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 6,46</t>
+          <t>-9,03; 6,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>32,92; 107,44</t>
+          <t>33,27; 110,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,63; 111,21</t>
+          <t>34,82; 106,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,19; 71,95</t>
+          <t>12,69; 75,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-50,74; 45,69</t>
+          <t>-51,98; 42,25</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,86; 15,71</t>
+          <t>8,16; 15,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,52; 13,53</t>
+          <t>6,15; 13,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,29; 11,54</t>
+          <t>4,4; 11,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 7,78</t>
+          <t>-1,09; 7,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>49,27; 125,04</t>
+          <t>52,48; 118,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,28; 101,31</t>
+          <t>36,93; 102,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,52; 85,78</t>
+          <t>27,04; 84,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 46,09</t>
+          <t>-4,66; 46,64</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,76; 14,89</t>
+          <t>10,9; 15,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,95; 11,99</t>
+          <t>8,0; 12,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,03; 9,93</t>
+          <t>6,3; 10,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,75; 8,96</t>
+          <t>1,78; 9,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>64,22; 100,58</t>
+          <t>65,49; 101,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,52; 76,17</t>
+          <t>45,47; 76,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,13; 67,32</t>
+          <t>38,96; 69,69</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,21; 62,96</t>
+          <t>10,39; 64,82</t>
         </is>
       </c>
     </row>
